--- a/data/LM3_LMI_Summary.xlsx
+++ b/data/LM3_LMI_Summary.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dafha\Work Colleague\Mba rida\Event\MAILER\without raw data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dafha\Work Colleague\OS\Mba rida\Event\MAILER\new begin_stk\without raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3535CE9-EE81-4833-A97C-F6906F908383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{466ABA57-B8F4-4EB4-929D-761A43A7BCBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{F673BAF6-C00D-42EA-9313-7CB2BD08351B}"/>
   </bookViews>
@@ -28,6 +28,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -395,6 +397,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -404,7 +407,6 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -704,30 +706,30 @@
   <dimension ref="A1:N21"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.7109375" style="5"/>
-    <col min="7" max="7" width="14.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.7109375" style="2"/>
+    <col min="7" max="7" width="14.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.7109375" style="14"/>
-    <col min="10" max="16384" width="8.7109375" style="5"/>
+    <col min="10" max="16384" width="8.7109375" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="4"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="32" t="s">
@@ -794,530 +796,530 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <v>30489.657888999998</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <v>27040.933605999999</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="5">
         <v>3448.724283</v>
       </c>
       <c r="F4" s="9">
         <v>11.31112817190456</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="5">
         <v>21025.047198</v>
       </c>
       <c r="H4" s="9">
         <v>68.957963629973619</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="5">
         <v>9464.6106909999999</v>
       </c>
       <c r="J4" s="9">
         <v>31.042036370026388</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="2">
         <v>692</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4" s="2">
         <v>639</v>
       </c>
       <c r="M4" s="9">
         <v>92.341040462427742</v>
       </c>
-      <c r="N4" s="5">
+      <c r="N4" s="2">
         <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="5">
         <v>7375.058051</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="5">
         <v>6566.0781639999996</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="5">
         <v>808.97988699999996</v>
       </c>
       <c r="F5" s="9">
         <v>10.969132465205595</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="5">
         <v>5474.2686109999995</v>
       </c>
       <c r="H5" s="9">
         <v>74.226786733668234</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="5">
         <v>1900.78944</v>
       </c>
       <c r="J5" s="9">
         <v>25.773213266331751</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="2">
         <v>503</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5" s="2">
         <v>367</v>
       </c>
       <c r="M5" s="9">
         <v>72.962226640159045</v>
       </c>
-      <c r="N5" s="5">
+      <c r="N5" s="2">
         <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="5">
         <v>15205.298824</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="5">
         <v>13617.758693</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="5">
         <v>1587.540131</v>
       </c>
       <c r="F6" s="9">
         <v>10.440703266510166</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="5">
         <v>5529.0779089999996</v>
       </c>
       <c r="H6" s="9">
         <v>36.362836225703894</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="5">
         <v>9676.2209149999999</v>
       </c>
       <c r="J6" s="9">
         <v>63.637163774296113</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6" s="2">
         <v>649</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6" s="2">
         <v>472</v>
       </c>
       <c r="M6" s="9">
         <v>72.727272727272734</v>
       </c>
-      <c r="N6" s="5">
+      <c r="N6" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="5">
         <v>16586.203966000001</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="5">
         <v>14531.495758999999</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="5">
         <v>2054.7082070000001</v>
       </c>
       <c r="F7" s="9">
         <v>12.388055827674247</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="5">
         <v>13037.915650000001</v>
       </c>
       <c r="H7" s="9">
         <v>78.606989741150997</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7" s="5">
         <v>3548.2883160000001</v>
       </c>
       <c r="J7" s="9">
         <v>21.393010258849003</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="2">
         <v>687</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7" s="2">
         <v>593</v>
       </c>
       <c r="M7" s="9">
         <v>86.317321688500726</v>
       </c>
-      <c r="N7" s="5">
+      <c r="N7" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="5">
         <v>27370.078647999999</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="5">
         <v>23354.809255</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="5">
         <v>4015.269393</v>
       </c>
       <c r="F8" s="9">
         <v>14.670288107825391</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="5">
         <v>15496.772428999999</v>
       </c>
       <c r="H8" s="9">
         <v>56.619393127437675</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8" s="5">
         <v>11873.306219</v>
       </c>
       <c r="J8" s="9">
         <v>43.380606872562325</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K8" s="2">
         <v>710</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L8" s="2">
         <v>621</v>
       </c>
       <c r="M8" s="9">
         <v>87.464788732394368</v>
       </c>
-      <c r="N8" s="5">
+      <c r="N8" s="2">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="5">
         <v>8607.5751299999993</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="5">
         <v>7810.6311919999998</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="5">
         <v>796.943938</v>
       </c>
       <c r="F9" s="9">
         <v>9.2586347021521735</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="5">
         <v>7857.7461179999991</v>
       </c>
       <c r="H9" s="9">
         <v>91.288731138847453</v>
       </c>
-      <c r="I9" s="4">
+      <c r="I9" s="5">
         <v>749.82901200000003</v>
       </c>
       <c r="J9" s="9">
         <v>8.7112688611525382</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9" s="2">
         <v>533</v>
       </c>
-      <c r="L9" s="5">
+      <c r="L9" s="2">
         <v>430</v>
       </c>
       <c r="M9" s="9">
         <v>80.675422138836765</v>
       </c>
-      <c r="N9" s="5">
+      <c r="N9" s="2">
         <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="5">
         <v>13666.99748</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="5">
         <v>12940.475031</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="5">
         <v>726.52244900000005</v>
       </c>
       <c r="F10" s="9">
         <v>5.3158892438750929</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="5">
         <v>8323.6435410000013</v>
       </c>
       <c r="H10" s="9">
         <v>60.903234621800785</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I10" s="5">
         <v>5343.3539389999996</v>
       </c>
       <c r="J10" s="9">
         <v>39.096765378199215</v>
       </c>
-      <c r="K10" s="5">
+      <c r="K10" s="2">
         <v>665</v>
       </c>
-      <c r="L10" s="5">
+      <c r="L10" s="2">
         <v>506</v>
       </c>
       <c r="M10" s="9">
         <v>76.090225563909769</v>
       </c>
-      <c r="N10" s="5">
+      <c r="N10" s="2">
         <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="5">
         <v>12067.6016</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="5">
         <v>10823.940821</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="5">
         <v>1243.660779</v>
       </c>
       <c r="F11" s="9">
         <v>10.305782542572503</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="5">
         <v>4581.8013940000001</v>
       </c>
       <c r="H11" s="9">
         <v>37.967788015142965</v>
       </c>
-      <c r="I11" s="4">
+      <c r="I11" s="5">
         <v>7485.8002059999999</v>
       </c>
       <c r="J11" s="9">
         <v>62.032211984857042</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K11" s="2">
         <v>542</v>
       </c>
-      <c r="L11" s="5">
+      <c r="L11" s="2">
         <v>333</v>
       </c>
       <c r="M11" s="9">
         <v>61.43911439114391</v>
       </c>
-      <c r="N11" s="5">
+      <c r="N11" s="2">
         <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="5">
         <v>7201.8989449999999</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="5">
         <v>5723.8817740000004</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="5">
         <v>1478.017171</v>
       </c>
       <c r="F12" s="9">
         <v>20.522603583963505</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="5">
         <v>5282.1011989999997</v>
       </c>
       <c r="H12" s="9">
         <v>73.343172951172249</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I12" s="5">
         <v>1919.797746</v>
       </c>
       <c r="J12" s="9">
         <v>26.656827048827747</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K12" s="2">
         <v>478</v>
       </c>
-      <c r="L12" s="5">
+      <c r="L12" s="2">
         <v>364</v>
       </c>
       <c r="M12" s="9">
         <v>76.15062761506276</v>
       </c>
-      <c r="N12" s="5">
+      <c r="N12" s="2">
         <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="5">
         <v>7696.486922</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="5">
         <v>6433.9005429999997</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="5">
         <v>1262.5863790000001</v>
       </c>
       <c r="F13" s="9">
         <v>16.404710250217715</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="5">
         <v>5253.3220440000005</v>
       </c>
       <c r="H13" s="9">
         <v>68.256103040773809</v>
       </c>
-      <c r="I13" s="4">
+      <c r="I13" s="5">
         <v>2443.164878</v>
       </c>
       <c r="J13" s="9">
         <v>31.743896959226198</v>
       </c>
-      <c r="K13" s="5">
+      <c r="K13" s="2">
         <v>551</v>
       </c>
-      <c r="L13" s="5">
+      <c r="L13" s="2">
         <v>437</v>
       </c>
       <c r="M13" s="9">
         <v>79.310344827586206</v>
       </c>
-      <c r="N13" s="5">
+      <c r="N13" s="2">
         <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="5">
         <v>6060.8929539999999</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="5">
         <v>5713.7567900000004</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="5">
         <v>347.13616400000001</v>
       </c>
       <c r="F14" s="9">
         <v>5.7274755821401033</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="5">
         <v>4750.4390229999999</v>
       </c>
       <c r="H14" s="9">
         <v>78.378533642717755</v>
       </c>
-      <c r="I14" s="4">
+      <c r="I14" s="5">
         <v>1310.453931</v>
       </c>
       <c r="J14" s="9">
         <v>21.621466357282245</v>
       </c>
-      <c r="K14" s="5">
+      <c r="K14" s="2">
         <v>548</v>
       </c>
-      <c r="L14" s="5">
+      <c r="L14" s="2">
         <v>422</v>
       </c>
       <c r="M14" s="9">
         <v>77.007299270072991</v>
       </c>
-      <c r="N14" s="5">
+      <c r="N14" s="2">
         <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="5">
         <v>9964.1631770000004</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="5">
         <v>9087.6697879999992</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="5">
         <v>876.49338899999998</v>
       </c>
       <c r="F15" s="9">
         <v>8.7964575994016769</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="5">
         <v>9964.1631770000004</v>
       </c>
       <c r="H15" s="9">
         <v>100</v>
       </c>
-      <c r="I15" s="4">
+      <c r="I15" s="5">
         <v>0</v>
       </c>
       <c r="J15" s="9">
         <v>0</v>
       </c>
-      <c r="K15" s="5">
+      <c r="K15" s="2">
         <v>657</v>
       </c>
-      <c r="L15" s="5">
+      <c r="L15" s="2">
         <v>549</v>
       </c>
       <c r="M15" s="9">
         <v>83.561643835616437</v>
       </c>
-      <c r="N15" s="5">
+      <c r="N15" s="2">
         <v>46</v>
       </c>
     </row>
@@ -1325,41 +1327,41 @@
       <c r="A16" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4">
+      <c r="B16" s="4"/>
+      <c r="C16" s="5">
         <v>253.80216100000001</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="5">
         <v>253.80216100000001</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="5">
         <v>0</v>
       </c>
       <c r="F16" s="9">
         <v>0</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G16" s="5">
         <v>253.80216100000001</v>
       </c>
       <c r="H16" s="9">
         <v>100</v>
       </c>
-      <c r="I16" s="4">
+      <c r="I16" s="5">
         <v>0</v>
       </c>
       <c r="J16" s="9">
         <v>0</v>
       </c>
-      <c r="K16" s="5">
-        <v>0</v>
-      </c>
-      <c r="L16" s="5">
+      <c r="K16" s="2">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2">
         <v>0</v>
       </c>
       <c r="M16" s="9">
         <v>0</v>
       </c>
-      <c r="N16" s="5">
+      <c r="N16" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1367,41 +1369,41 @@
       <c r="A17" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4">
+      <c r="B17" s="4"/>
+      <c r="C17" s="5">
         <v>106.537983</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="5">
         <v>106.537983</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="5">
         <v>0</v>
       </c>
       <c r="F17" s="9">
         <v>0</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="5">
         <v>106.537983</v>
       </c>
       <c r="H17" s="9">
         <v>100</v>
       </c>
-      <c r="I17" s="4">
+      <c r="I17" s="5">
         <v>0</v>
       </c>
       <c r="J17" s="9">
         <v>0</v>
       </c>
-      <c r="K17" s="5">
+      <c r="K17" s="2">
         <v>4</v>
       </c>
-      <c r="L17" s="5">
+      <c r="L17" s="2">
         <v>0</v>
       </c>
       <c r="M17" s="9">
         <v>0</v>
       </c>
-      <c r="N17" s="5">
+      <c r="N17" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1409,41 +1411,41 @@
       <c r="A18" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4">
-        <v>0</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
-      <c r="E18" s="4">
+      <c r="B18" s="4"/>
+      <c r="C18" s="5">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5">
         <v>0</v>
       </c>
       <c r="F18" s="9">
         <v>0</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18" s="5">
         <v>0</v>
       </c>
       <c r="H18" s="9">
         <v>0</v>
       </c>
-      <c r="I18" s="4">
+      <c r="I18" s="5">
         <v>0</v>
       </c>
       <c r="J18" s="9">
         <v>0</v>
       </c>
-      <c r="K18" s="5">
+      <c r="K18" s="2">
         <v>1</v>
       </c>
-      <c r="L18" s="5">
+      <c r="L18" s="2">
         <v>0</v>
       </c>
       <c r="M18" s="9">
         <v>0</v>
       </c>
-      <c r="N18" s="5">
+      <c r="N18" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1511,7 +1513,7 @@
   <dimension ref="A1:N36"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.140625" style="18" customWidth="1"/>
     <col min="3" max="5" width="8.85546875" style="14" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.85546875" style="18" bestFit="1" customWidth="1"/>
@@ -1523,7 +1525,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>67</v>
       </c>
       <c r="B1" s="15"/>
@@ -1601,19 +1603,19 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
+      <c r="A4" s="4">
         <v>31</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <v>2077.6303739999998</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <v>1977.219926</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="5">
         <v>100.410448</v>
       </c>
       <c r="F4" s="9">
@@ -1631,33 +1633,33 @@
       <c r="J4" s="9">
         <v>0</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="5">
         <v>70</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="5">
         <v>63</v>
       </c>
       <c r="M4" s="9">
         <v>90</v>
       </c>
-      <c r="N4" s="3">
+      <c r="N4" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
+      <c r="A5" s="4">
         <v>32</v>
       </c>
       <c r="B5" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="5">
         <v>6478.561498</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="5">
         <v>6173.2350960000003</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="5">
         <v>305.32640199999997</v>
       </c>
       <c r="F5" s="9">
@@ -1675,33 +1677,33 @@
       <c r="J5" s="9">
         <v>1.6904810025788785E-3</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="5">
         <v>43</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="5">
         <v>42</v>
       </c>
       <c r="M5" s="9">
         <v>97.674418604651152</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
+      <c r="A6" s="4">
         <v>33</v>
       </c>
       <c r="B6" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="5">
         <v>7570.2954950000003</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="5">
         <v>7396.5814950000004</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="5">
         <v>173.714</v>
       </c>
       <c r="F6" s="9">
@@ -1719,33 +1721,33 @@
       <c r="J6" s="9">
         <v>1.020089477282644E-3</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6" s="5">
         <v>79</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6" s="5">
         <v>59</v>
       </c>
       <c r="M6" s="9">
         <v>74.683544303797461</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N6" s="4">
         <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
+      <c r="A7" s="4">
         <v>34</v>
       </c>
       <c r="B7" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="5">
         <v>2918.5814759999998</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="5">
         <v>2740.697369</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="5">
         <v>177.884107</v>
       </c>
       <c r="F7" s="9">
@@ -1763,33 +1765,33 @@
       <c r="J7" s="9">
         <v>2.4547801480715452E-3</v>
       </c>
-      <c r="K7" s="4">
+      <c r="K7" s="5">
         <v>58</v>
       </c>
-      <c r="L7" s="4">
+      <c r="L7" s="5">
         <v>56</v>
       </c>
       <c r="M7" s="9">
         <v>96.551724137931032</v>
       </c>
-      <c r="N7" s="3">
+      <c r="N7" s="4">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
+      <c r="A8" s="4">
         <v>35</v>
       </c>
       <c r="B8" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="5">
         <v>7318.7494479999996</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="5">
         <v>6670.6663829999998</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="5">
         <v>648.08306500000003</v>
       </c>
       <c r="F8" s="9">
@@ -1807,16 +1809,16 @@
       <c r="J8" s="9">
         <v>0.15824736047410046</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8" s="5">
         <v>473</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L8" s="5">
         <v>411</v>
       </c>
       <c r="M8" s="9">
         <v>86.892177589852011</v>
       </c>
-      <c r="N8" s="3">
+      <c r="N8" s="4">
         <v>37</v>
       </c>
     </row>
@@ -1865,19 +1867,19 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
+      <c r="A10" s="4">
         <v>80</v>
       </c>
       <c r="B10" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="5">
         <v>3191.8300709999999</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="5">
         <v>3152.4714410000001</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="5">
         <v>39.358629999999998</v>
       </c>
       <c r="F10" s="9">
@@ -1895,33 +1897,33 @@
       <c r="J10" s="9">
         <v>1.0980028393270649E-3</v>
       </c>
-      <c r="K10" s="4">
+      <c r="K10" s="5">
         <v>27</v>
       </c>
-      <c r="L10" s="4">
+      <c r="L10" s="5">
         <v>22</v>
       </c>
       <c r="M10" s="9">
         <v>81.481481481481481</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="4">
         <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
+      <c r="A11" s="4">
         <v>82</v>
       </c>
       <c r="B11" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="5">
         <v>4504.0759390000003</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="5">
         <v>4365.2937309999998</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="5">
         <v>138.782208</v>
       </c>
       <c r="F11" s="9">
@@ -1939,16 +1941,16 @@
       <c r="J11" s="9">
         <v>0</v>
       </c>
-      <c r="K11" s="4">
+      <c r="K11" s="5">
         <v>31</v>
       </c>
-      <c r="L11" s="4">
+      <c r="L11" s="5">
         <v>28</v>
       </c>
       <c r="M11" s="9">
         <v>90.322580645161281</v>
       </c>
-      <c r="N11" s="3">
+      <c r="N11" s="4">
         <v>29</v>
       </c>
     </row>
@@ -1997,19 +1999,19 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="3">
+      <c r="A13" s="4">
         <v>11</v>
       </c>
       <c r="B13" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="5">
         <v>19411.156064999999</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="5">
         <v>18202.947758999999</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="5">
         <v>1208.208306</v>
       </c>
       <c r="F13" s="9">
@@ -2027,33 +2029,33 @@
       <c r="J13" s="9">
         <v>52.42419237243994</v>
       </c>
-      <c r="K13" s="4">
+      <c r="K13" s="5">
         <v>828</v>
       </c>
-      <c r="L13" s="4">
+      <c r="L13" s="5">
         <v>751</v>
       </c>
       <c r="M13" s="9">
         <v>90.700483091787447</v>
       </c>
-      <c r="N13" s="3">
+      <c r="N13" s="4">
         <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="3">
+      <c r="A14" s="4">
         <v>17</v>
       </c>
       <c r="B14" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="5">
         <v>30185.058010000001</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="5">
         <v>26653.091259000001</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="5">
         <v>3531.9667509999999</v>
       </c>
       <c r="F14" s="9">
@@ -2071,33 +2073,33 @@
       <c r="J14" s="9">
         <v>65.768557541409876</v>
       </c>
-      <c r="K14" s="4">
+      <c r="K14" s="5">
         <v>676</v>
       </c>
-      <c r="L14" s="4">
+      <c r="L14" s="5">
         <v>567</v>
       </c>
       <c r="M14" s="9">
         <v>83.875739644970409</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="4">
         <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="3">
+      <c r="A15" s="4">
         <v>21</v>
       </c>
       <c r="B15" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="5">
         <v>13203.015445999999</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="5">
         <v>7863.4720939999997</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="5">
         <v>5339.5433519999997</v>
       </c>
       <c r="F15" s="9">
@@ -2115,33 +2117,33 @@
       <c r="J15" s="9">
         <v>160.97701069406301</v>
       </c>
-      <c r="K15" s="4">
+      <c r="K15" s="5">
         <v>228</v>
       </c>
-      <c r="L15" s="4">
+      <c r="L15" s="5">
         <v>194</v>
       </c>
       <c r="M15" s="9">
         <v>85.087719298245617</v>
       </c>
-      <c r="N15" s="3">
+      <c r="N15" s="4">
         <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="3">
+      <c r="A16" s="4">
         <v>23</v>
       </c>
       <c r="B16" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="5">
         <v>19594.470744999999</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="5">
         <v>15714.653826</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="5">
         <v>3879.8169189999999</v>
       </c>
       <c r="F16" s="9">
@@ -2159,33 +2161,33 @@
       <c r="J16" s="9">
         <v>113.02448333044364</v>
       </c>
-      <c r="K16" s="4">
+      <c r="K16" s="5">
         <v>785</v>
       </c>
-      <c r="L16" s="4">
+      <c r="L16" s="5">
         <v>673</v>
       </c>
       <c r="M16" s="9">
         <v>85.732484076433124</v>
       </c>
-      <c r="N16" s="3">
+      <c r="N16" s="4">
         <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" s="3">
+      <c r="A17" s="4">
         <v>24</v>
       </c>
       <c r="B17" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="5">
         <v>7564.0302380000003</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="5">
         <v>7176.9118189999999</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="5">
         <v>387.11841900000002</v>
       </c>
       <c r="F17" s="9">
@@ -2203,16 +2205,16 @@
       <c r="J17" s="9">
         <v>51.944040760163837</v>
       </c>
-      <c r="K17" s="4">
+      <c r="K17" s="5">
         <v>728</v>
       </c>
-      <c r="L17" s="4">
+      <c r="L17" s="5">
         <v>551</v>
       </c>
       <c r="M17" s="9">
         <v>75.686813186813183</v>
       </c>
-      <c r="N17" s="3">
+      <c r="N17" s="4">
         <v>39</v>
       </c>
     </row>
@@ -2261,19 +2263,19 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="3">
+      <c r="A19" s="4">
         <v>14</v>
       </c>
       <c r="B19" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="5">
         <v>12518.372432</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="5">
         <v>12108.629548999999</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="5">
         <v>409.74288300000001</v>
       </c>
       <c r="F19" s="9">
@@ -2291,33 +2293,33 @@
       <c r="J19" s="9">
         <v>46.319067064890248</v>
       </c>
-      <c r="K19" s="4">
+      <c r="K19" s="5">
         <v>748</v>
       </c>
-      <c r="L19" s="4">
+      <c r="L19" s="5">
         <v>609</v>
       </c>
       <c r="M19" s="9">
         <v>81.417112299465245</v>
       </c>
-      <c r="N19" s="3">
+      <c r="N19" s="4">
         <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" s="3">
+      <c r="A20" s="4">
         <v>19</v>
       </c>
       <c r="B20" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="5">
         <v>18069.246171999999</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="5">
         <v>16531.173697999999</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="5">
         <v>1538.0724740000001</v>
       </c>
       <c r="F20" s="9">
@@ -2335,16 +2337,16 @@
       <c r="J20" s="9">
         <v>194.84411905864593</v>
       </c>
-      <c r="K20" s="4">
+      <c r="K20" s="5">
         <v>773</v>
       </c>
-      <c r="L20" s="4">
+      <c r="L20" s="5">
         <v>505</v>
       </c>
       <c r="M20" s="9">
         <v>65.329883570504535</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20" s="4">
         <v>61</v>
       </c>
     </row>
@@ -2393,19 +2395,19 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A22" s="3">
+      <c r="A22" s="4">
         <v>86</v>
       </c>
       <c r="B22" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="5">
         <v>1031.0920610000001</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="5">
         <v>1031.0920610000001</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="5">
         <v>0</v>
       </c>
       <c r="F22" s="9">
@@ -2423,33 +2425,33 @@
       <c r="J22" s="9">
         <v>8.9566464847471456E-3</v>
       </c>
-      <c r="K22" s="4">
-        <v>0</v>
-      </c>
-      <c r="L22" s="4">
+      <c r="K22" s="5">
+        <v>0</v>
+      </c>
+      <c r="L22" s="5">
         <v>0</v>
       </c>
       <c r="M22" s="9">
         <v>0</v>
       </c>
-      <c r="N22" s="3">
+      <c r="N22" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="3">
+      <c r="A23" s="4">
         <v>87</v>
       </c>
       <c r="B23" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="5">
         <v>517.85186199999998</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="5">
         <v>503.01942500000001</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="5">
         <v>14.832437000000001</v>
       </c>
       <c r="F23" s="9">
@@ -2467,33 +2469,33 @@
       <c r="J23" s="9">
         <v>0</v>
       </c>
-      <c r="K23" s="4">
+      <c r="K23" s="5">
         <v>32</v>
       </c>
-      <c r="L23" s="4">
+      <c r="L23" s="5">
         <v>13</v>
       </c>
       <c r="M23" s="9">
         <v>40.625</v>
       </c>
-      <c r="N23" s="3">
+      <c r="N23" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" s="3">
+      <c r="A24" s="4">
         <v>88</v>
       </c>
       <c r="B24" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="5">
         <v>937.89369699999997</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="5">
         <v>907.63603999999998</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="5">
         <v>30.257656999999998</v>
       </c>
       <c r="F24" s="9">
@@ -2511,16 +2513,16 @@
       <c r="J24" s="9">
         <v>0</v>
       </c>
-      <c r="K24" s="4">
+      <c r="K24" s="5">
         <v>6</v>
       </c>
-      <c r="L24" s="4">
+      <c r="L24" s="5">
         <v>3</v>
       </c>
       <c r="M24" s="9">
         <v>50</v>
       </c>
-      <c r="N24" s="3">
+      <c r="N24" s="4">
         <v>1</v>
       </c>
     </row>
@@ -2569,19 +2571,19 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" s="3">
+      <c r="A26" s="4">
         <v>51</v>
       </c>
       <c r="B26" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="5">
         <v>970.02075500000001</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="5">
         <v>953.86760800000002</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="5">
         <v>16.153147000000001</v>
       </c>
       <c r="F26" s="9">
@@ -2599,33 +2601,33 @@
       <c r="J26" s="9">
         <v>4.5511406713198985E-3</v>
       </c>
-      <c r="K26" s="4">
+      <c r="K26" s="5">
         <v>117</v>
       </c>
-      <c r="L26" s="4">
+      <c r="L26" s="5">
         <v>50</v>
       </c>
       <c r="M26" s="9">
         <v>42.735042735042732</v>
       </c>
-      <c r="N26" s="3">
+      <c r="N26" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" s="3">
+      <c r="A27" s="4">
         <v>57</v>
       </c>
       <c r="B27" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="5">
         <v>822.236355</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="5">
         <v>638.99902199999997</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="5">
         <v>183.23733300000001</v>
       </c>
       <c r="F27" s="9">
@@ -2643,33 +2645,33 @@
       <c r="J27" s="9">
         <v>5.4678265978795526E-3</v>
       </c>
-      <c r="K27" s="4">
+      <c r="K27" s="5">
         <v>1136</v>
       </c>
-      <c r="L27" s="4">
+      <c r="L27" s="5">
         <v>826</v>
       </c>
       <c r="M27" s="9">
         <v>72.711267605633793</v>
       </c>
-      <c r="N27" s="3">
+      <c r="N27" s="4">
         <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28" s="3">
+      <c r="A28" s="4">
         <v>85</v>
       </c>
       <c r="B28" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="5">
         <v>554.06975999999997</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="5">
         <v>498.36716699999999</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="5">
         <v>55.702593</v>
       </c>
       <c r="F28" s="9">
@@ -2687,33 +2689,33 @@
       <c r="J28" s="9">
         <v>4.0607939922967669</v>
       </c>
-      <c r="K28" s="4">
+      <c r="K28" s="5">
         <v>24</v>
       </c>
-      <c r="L28" s="4">
+      <c r="L28" s="5">
         <v>24</v>
       </c>
       <c r="M28" s="9">
         <v>100</v>
       </c>
-      <c r="N28" s="3">
+      <c r="N28" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29" s="3">
+      <c r="A29" s="4">
         <v>13</v>
       </c>
       <c r="B29" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="5">
         <v>329.45654500000001</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="5">
         <v>310.89843999999999</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="5">
         <v>18.558105000000001</v>
       </c>
       <c r="F29" s="9">
@@ -2731,33 +2733,33 @@
       <c r="J29" s="9">
         <v>0</v>
       </c>
-      <c r="K29" s="4">
+      <c r="K29" s="5">
         <v>57</v>
       </c>
-      <c r="L29" s="4">
+      <c r="L29" s="5">
         <v>48</v>
       </c>
       <c r="M29" s="9">
         <v>84.210526315789465</v>
       </c>
-      <c r="N29" s="3">
+      <c r="N29" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A30" s="3">
+      <c r="A30" s="4">
         <v>62</v>
       </c>
       <c r="B30" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="5">
         <v>1061.80413</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="5">
         <v>916.07911300000001</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E30" s="5">
         <v>145.72501700000001</v>
       </c>
       <c r="F30" s="9">
@@ -2775,33 +2777,33 @@
       <c r="J30" s="9">
         <v>1.01826697907536E-2</v>
       </c>
-      <c r="K30" s="4">
+      <c r="K30" s="5">
         <v>223</v>
       </c>
-      <c r="L30" s="4">
+      <c r="L30" s="5">
         <v>169</v>
       </c>
       <c r="M30" s="9">
         <v>75.784753363228702</v>
       </c>
-      <c r="N30" s="3">
+      <c r="N30" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A31" s="3">
+      <c r="A31" s="4">
         <v>71</v>
       </c>
       <c r="B31" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="5">
         <v>1801.7216189999999</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="5">
         <v>1497.6337020000001</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="5">
         <v>304.087917</v>
       </c>
       <c r="F31" s="9">
@@ -2819,16 +2821,16 @@
       <c r="J31" s="9">
         <v>8.705083163307669E-4</v>
       </c>
-      <c r="K31" s="4">
+      <c r="K31" s="5">
         <v>78</v>
       </c>
-      <c r="L31" s="4">
+      <c r="L31" s="5">
         <v>73</v>
       </c>
       <c r="M31" s="9">
         <v>93.589743589743591</v>
       </c>
-      <c r="N31" s="3">
+      <c r="N31" s="4">
         <v>6</v>
       </c>
     </row>
@@ -2877,19 +2879,19 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A33" s="3">
+      <c r="A33" s="4">
         <v>97</v>
       </c>
       <c r="B33" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="5">
         <v>6.1895480000000003</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="5">
         <v>6.1895480000000003</v>
       </c>
-      <c r="E33" s="4">
+      <c r="E33" s="5">
         <v>0</v>
       </c>
       <c r="F33" s="9">
@@ -2907,33 +2909,33 @@
       <c r="J33" s="9">
         <v>0</v>
       </c>
-      <c r="K33" s="4">
-        <v>0</v>
-      </c>
-      <c r="L33" s="4">
+      <c r="K33" s="5">
+        <v>0</v>
+      </c>
+      <c r="L33" s="5">
         <v>0</v>
       </c>
       <c r="M33" s="9">
         <v>0</v>
       </c>
-      <c r="N33" s="3">
+      <c r="N33" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A34" s="3">
+      <c r="A34" s="4">
         <v>98</v>
       </c>
       <c r="B34" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="C34" s="4">
-        <v>0</v>
-      </c>
-      <c r="D34" s="4">
-        <v>0</v>
-      </c>
-      <c r="E34" s="4">
+      <c r="C34" s="5">
+        <v>0</v>
+      </c>
+      <c r="D34" s="5">
+        <v>0</v>
+      </c>
+      <c r="E34" s="5">
         <v>0</v>
       </c>
       <c r="F34" s="9">
@@ -2951,33 +2953,33 @@
       <c r="J34" s="9">
         <v>0</v>
       </c>
-      <c r="K34" s="4">
-        <v>0</v>
-      </c>
-      <c r="L34" s="4">
+      <c r="K34" s="5">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5">
         <v>0</v>
       </c>
       <c r="M34" s="9">
         <v>0</v>
       </c>
-      <c r="N34" s="3">
+      <c r="N34" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A35" s="3">
+      <c r="A35" s="4">
         <v>99</v>
       </c>
       <c r="B35" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="5">
         <v>14.843989000000001</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="5">
         <v>14.843989000000001</v>
       </c>
-      <c r="E35" s="4">
+      <c r="E35" s="5">
         <v>0</v>
       </c>
       <c r="F35" s="9">
@@ -2995,16 +2997,16 @@
       <c r="J35" s="9">
         <v>0</v>
       </c>
-      <c r="K35" s="4">
-        <v>0</v>
-      </c>
-      <c r="L35" s="4">
+      <c r="K35" s="5">
+        <v>0</v>
+      </c>
+      <c r="L35" s="5">
         <v>0</v>
       </c>
       <c r="M35" s="9">
         <v>0</v>
       </c>
-      <c r="N35" s="3">
+      <c r="N35" s="4">
         <v>0</v>
       </c>
     </row>
